--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XVIII/LTAIPT_A63F18.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XVIII/LTAIPT_A63F18.xlsx
@@ -4,21 +4,23 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
+    <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Hidden_113">Hidden_1!$A$1:$A$2</definedName>
+    <definedName name="Hidden_17">Hidden_1!$A$1:$A$2</definedName>
+    <definedName name="Hidden_214">Hidden_2!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="93">
   <si>
     <t>48967</t>
   </si>
@@ -44,12 +46,12 @@
     <t>4</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -80,6 +82,9 @@
     <t>436088</t>
   </si>
   <si>
+    <t>571929</t>
+  </si>
+  <si>
     <t>436071</t>
   </si>
   <si>
@@ -176,10 +181,13 @@
     <t xml:space="preserve">Segundo apellido del (la) servidor(a) público(a) </t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Clave o nivel del puesto</t>
   </si>
   <si>
-    <t>Denominación del puesto</t>
+    <t>Denominación del puesto (de acuerdo con el catálogo que en su caso regule la actividad del sujeto obligado) (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Denominación del cargo</t>
@@ -251,7 +259,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Ver nota</t>
@@ -260,25 +268,31 @@
     <t/>
   </si>
   <si>
-    <t>Contraloría Interna</t>
-  </si>
-  <si>
-    <t>29/04/2021</t>
-  </si>
-  <si>
-    <t>1B82AD2FC901F5D5C129B63072B4AEDB</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>22/07/2022</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de abril de 2022 al 30 de junio de 2022 la Contraloría  Interna del Colegio de Bachilleres del Estado de Tlaxcala  no ha emitido alguna sanción administrativa a servidores públicos de esta Dependencia o Entidad Pública.</t>
+    <t>24/04/2023</t>
+  </si>
+  <si>
+    <t>40211E49E8B8CC75F556902350D96096</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>Contraloria Interna</t>
+  </si>
+  <si>
+    <t>25/07/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de abril de 2023 al 30 de junio de 2023 la Contraloría  Interna del Colegio de Bachilleres del Estado de Tlaxcala  no ha emitido alguna sanción administrativa a servidores públicos de esta Dependencia o Entidad Pública.</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
   <si>
     <t>Federal</t>
@@ -677,49 +691,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AG8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="56.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="32" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="53.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="58.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="48.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="20" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="213.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="126.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="56.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="32" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="53.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="208.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -736,7 +751,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -751,7 +766,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -771,7 +786,7 @@
         <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I4" t="s">
         <v>6</v>
@@ -783,70 +798,73 @@
         <v>6</v>
       </c>
       <c r="L4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" t="s">
         <v>8</v>
-      </c>
-      <c r="M4" t="s">
-        <v>6</v>
-      </c>
-      <c r="N4" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" t="s">
-        <v>6</v>
       </c>
       <c r="P4" t="s">
         <v>6</v>
       </c>
       <c r="Q4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R4" t="s">
         <v>7</v>
       </c>
-      <c r="R4" t="s">
-        <v>8</v>
-      </c>
       <c r="S4" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" t="s">
         <v>6</v>
       </c>
-      <c r="T4" t="s">
-        <v>8</v>
-      </c>
       <c r="U4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W4" t="s">
         <v>7</v>
       </c>
       <c r="X4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y4" t="s">
         <v>10</v>
       </c>
       <c r="Z4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA4" t="s">
         <v>11</v>
       </c>
       <c r="AB4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC4" t="s">
         <v>7</v>
       </c>
-      <c r="AC4" t="s">
-        <v>8</v>
-      </c>
       <c r="AD4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE4" t="s">
         <v>7</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>12</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -940,10 +958,13 @@
       <c r="AF5" t="s">
         <v>44</v>
       </c>
+      <c r="AG5" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -976,203 +997,210 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
+      <c r="AG6" s="4"/>
     </row>
-    <row r="7" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AE8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>86</v>
+      <c r="AG8" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="A6:AG6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1180,9 +1208,12 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N8:N198">
-      <formula1>Hidden_113</formula1>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H200">
+      <formula1>Hidden_17</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O8:O200">
+      <formula1>Hidden_214</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1196,12 +1227,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
